--- a/IOLCalcdata.xlsx
+++ b/IOLCalcdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokam\PycharmProjects\BarrettAutomate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A40343D-9A75-431C-8363-F6773C577E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87ADA0CC-545E-4490-91D3-7A8DF1E16560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4620" yWindow="0" windowWidth="17196" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,10 +54,6 @@
     <t>ld</t>
   </si>
   <si>
-    <t>Hoffer PACD</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>eye</t>
   </si>
   <si>
@@ -104,6 +100,10 @@
   </si>
   <si>
     <t>Haisis_SE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Hoffer_pACD</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -542,43 +542,43 @@
         <v>4</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="5" t="s">
+      <c r="I1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" s="8" t="s">
+      <c r="L1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -592,7 +592,7 @@
         <v>105737</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" s="7">
         <v>23.33</v>
@@ -610,10 +610,10 @@
         <v>0</v>
       </c>
       <c r="J2" s="10">
-        <v>1.88</v>
+        <v>5.37</v>
       </c>
       <c r="K2" s="10">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="L2" s="10">
         <v>0.4</v>

--- a/IOLCalcdata.xlsx
+++ b/IOLCalcdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokam\PycharmProjects\BarrettAutomate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87ADA0CC-545E-4490-91D3-7A8DF1E16560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D92CE348-AD2D-4BCA-86E0-1FEC4E7E9320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4620" yWindow="0" windowWidth="17196" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1200" yWindow="696" windowWidth="17196" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="36" r:id="rId1"/>
@@ -99,12 +99,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Haisis_SE</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Hoffer_pACD</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Haigis_SE</t>
   </si>
 </sst>
 </file>
@@ -560,7 +559,7 @@
         <v>15</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>9</v>
@@ -578,7 +577,7 @@
         <v>16</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">

--- a/IOLCalcdata.xlsx
+++ b/IOLCalcdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokam\PycharmProjects\BarrettAutomate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D92CE348-AD2D-4BCA-86E0-1FEC4E7E9320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C542833-AC32-4079-9050-3E95FBB3E440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1200" yWindow="696" windowWidth="17196" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2085" yWindow="150" windowWidth="20220" windowHeight="15330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="36" r:id="rId1"/>
@@ -42,9 +42,6 @@
     <t>attack01</t>
   </si>
   <si>
-    <t>KALADA</t>
-  </si>
-  <si>
     <t>Surgeon</t>
   </si>
   <si>
@@ -104,6 +101,10 @@
   </si>
   <si>
     <t>Haigis_SE</t>
+  </si>
+  <si>
+    <t>KALA</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -518,89 +519,89 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="13" style="1" customWidth="1"/>
-    <col min="2" max="4" width="13" style="2" customWidth="1"/>
-    <col min="5" max="8" width="13" style="7" customWidth="1"/>
-    <col min="9" max="9" width="13" style="6" customWidth="1"/>
-    <col min="10" max="12" width="13" style="2" customWidth="1"/>
-    <col min="13" max="14" width="13" style="9" customWidth="1"/>
-    <col min="15" max="16" width="13.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.125" style="1" customWidth="1"/>
+    <col min="2" max="4" width="9.125" style="2" customWidth="1"/>
+    <col min="5" max="8" width="9.125" style="7" customWidth="1"/>
+    <col min="9" max="9" width="9.125" style="6" customWidth="1"/>
+    <col min="10" max="12" width="9.125" style="2" customWidth="1"/>
+    <col min="13" max="14" width="9.125" style="9" customWidth="1"/>
+    <col min="15" max="16" width="9.125" style="1" customWidth="1"/>
     <col min="17" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="E1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="5" t="s">
+      <c r="I1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="8" t="s">
+      <c r="L1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C2" s="1">
         <v>105737</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" s="7">
         <v>23.33</v>
       </c>
       <c r="F2" s="7">
+        <v>44.25</v>
+      </c>
+      <c r="G2" s="7">
         <v>44.75</v>
-      </c>
-      <c r="G2" s="7">
-        <v>44.25</v>
       </c>
       <c r="H2" s="7">
         <v>2.1800000000000002</v>
@@ -609,22 +610,22 @@
         <v>0</v>
       </c>
       <c r="J2" s="10">
-        <v>5.37</v>
+        <v>5.64</v>
       </c>
       <c r="K2" s="10">
-        <v>1.9</v>
+        <v>-0.76900000000000002</v>
       </c>
       <c r="L2" s="10">
-        <v>0.4</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="M2" s="7">
-        <v>0.1</v>
+        <v>0.217</v>
       </c>
       <c r="N2" s="9">
         <v>21.5</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -633,49 +634,49 @@
       <c r="K3" s="10"/>
       <c r="L3" s="10"/>
     </row>
-    <row r="4" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="1"/>
       <c r="J4" s="10"/>
       <c r="K4" s="10"/>
       <c r="L4" s="10"/>
     </row>
-    <row r="5" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1"/>
       <c r="J5" s="10"/>
       <c r="K5" s="10"/>
       <c r="L5" s="10"/>
     </row>
-    <row r="6" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="1"/>
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
       <c r="L6" s="10"/>
     </row>
-    <row r="7" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1"/>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
       <c r="L7" s="10"/>
     </row>
-    <row r="8" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1"/>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
       <c r="L8" s="10"/>
     </row>
-    <row r="9" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="1"/>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
       <c r="L9" s="10"/>
     </row>
-    <row r="10" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="1"/>
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
       <c r="L10" s="10"/>
     </row>
-    <row r="11" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="1"/>
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
